--- a/data/trending_integrated_20260916_14.xlsx
+++ b/data/trending_integrated_20260916_14.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F2" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G2" t="n">
-        <v>1153</v>
+        <v>1169</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7458979650</v>
+        <v>7461644610</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13860</v>
+        <v>13790</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+29.53%</t>
+          <t>'+28.88%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>177088135070</v>
+        <v>177863535660</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16100</v>
+        <v>16010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.86%</t>
+          <t>'+13.22%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F4" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G4" t="n">
-        <v>1905</v>
+        <v>1944</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>600273265775</v>
+        <v>609502928935</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 자회사 인캡의 대규모 광통신 수주 임박 및 외국인/기관의 대량 순매수로 주가 상승 기대감 고조. 긍정적 전망.</t>
+          <t>외인/기관 대규모 순매수 및 미국 자회사 수주 기대감. 10만원 목표.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신수주', '외국인순매수', '기관순매수']</t>
+          <t>['대량순매수', '광통신수주', '미국자회사']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4400</v>
+        <v>4405</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.80%</t>
+          <t>'+6.92%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F5" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G5" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>312120237367</v>
+        <v>313456230529</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 장의 광케이블 상승 및 젠슨황의 구리값 언급에 따른 광통신 관련 기대감 존재. 주가 급등에 대한 희망적인 언급.</t>
+          <t>광케이블 관련 기대감 속 지지선 확보. 종가 예상 및 향후 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광케이블', '젠슨황', '주가상승']</t>
+          <t>['광케이블', '지지선', '종가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,70 +931,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7240</v>
+        <v>193700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.93%</t>
+          <t>'+3.53%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>67</v>
+        <v>318</v>
       </c>
       <c r="H6" t="n">
-        <v>0.79</v>
+        <v>75.66</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6900</v>
+        <v>187100</v>
       </c>
       <c r="K6" t="n">
-        <v>6770</v>
+        <v>187200</v>
       </c>
       <c r="L6" t="n">
-        <v>8590</v>
+        <v>195900</v>
       </c>
       <c r="M6" t="n">
-        <v>6660</v>
+        <v>186100</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7</v>
+        <v>75.67</v>
       </c>
       <c r="O6" t="n">
-        <v>79418881275</v>
+        <v>528693680200</v>
       </c>
       <c r="P6" t="n">
-        <v>10360</v>
+        <v>243500</v>
       </c>
       <c r="Q6" t="n">
-        <v>2965</v>
+        <v>61800</v>
       </c>
       <c r="R6" t="n">
-        <v>74000</v>
+        <v>-216000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['우선주', '배당', '괴리율']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>193500</v>
+        <v>7130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.42%</t>
+          <t>'+3.33%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>318</v>
+        <v>67</v>
       </c>
       <c r="H7" t="n">
-        <v>75.66</v>
+        <v>0.79</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>187100</v>
+        <v>6900</v>
       </c>
       <c r="K7" t="n">
-        <v>187200</v>
+        <v>6770</v>
       </c>
       <c r="L7" t="n">
-        <v>195900</v>
+        <v>8590</v>
       </c>
       <c r="M7" t="n">
-        <v>186100</v>
+        <v>6660</v>
       </c>
       <c r="N7" t="n">
-        <v>75.67</v>
+        <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>521632236100</v>
+        <v>79882537165</v>
       </c>
       <c r="P7" t="n">
-        <v>243500</v>
+        <v>10360</v>
       </c>
       <c r="Q7" t="n">
-        <v>61800</v>
+        <v>2965</v>
       </c>
       <c r="R7" t="n">
-        <v>-216000</v>
+        <v>74000</v>
       </c>
       <c r="S7" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['우선주', '배당', '괴리율']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1130,10 +1130,10 @@
         <v>0.82</v>
       </c>
       <c r="E8" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8" t="n">
         <v>164</v>
@@ -1162,7 +1162,7 @@
         <v>0.84</v>
       </c>
       <c r="O8" t="n">
-        <v>125385766920</v>
+        <v>126644075343</v>
       </c>
       <c r="P8" t="n">
         <v>6190</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1732000</v>
+        <v>1735000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.49%</t>
+          <t>'+2.66%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G9" t="n">
-        <v>1974</v>
+        <v>1946</v>
       </c>
       <c r="H9" t="n">
         <v>50.2</v>
@@ -1254,7 +1254,7 @@
         <v>50.27</v>
       </c>
       <c r="O9" t="n">
-        <v>3275164659500</v>
+        <v>3360563132500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 기대감으로 인한 주가 상승 전망. 외인 선물 매수가 긍정적 요인으로 언급됨.</t>
+          <t>외인 선물 대규모 매수 속 자사주 매입 및 소각 기대감. 그러나 '내가 팔면 오르는' 패턴 반복.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1299,70 +1299,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>251750</v>
+        <v>3430</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.31%</t>
+          <t>'+2.08%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>-1.34</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>89</v>
       </c>
       <c r="F10" t="n">
-        <v>445</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
-        <v>1531</v>
+        <v>203</v>
       </c>
       <c r="H10" t="n">
-        <v>46.56</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>248500</v>
+        <v>3360</v>
       </c>
       <c r="K10" t="n">
-        <v>248000</v>
+        <v>3570</v>
       </c>
       <c r="L10" t="n">
-        <v>254000</v>
+        <v>3910</v>
       </c>
       <c r="M10" t="n">
-        <v>247500</v>
+        <v>3345</v>
       </c>
       <c r="N10" t="n">
-        <v>46.57</v>
+        <v>1.34</v>
       </c>
       <c r="O10" t="n">
-        <v>1963483410750</v>
+        <v>103044712109</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>5100</v>
       </c>
       <c r="Q10" t="n">
-        <v>76700</v>
+        <v>966</v>
       </c>
       <c r="R10" t="n">
-        <v>-720000</v>
+        <v>-31000</v>
       </c>
       <c r="S10" t="n">
-        <v>754000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>전반적으로 정치 관련 언급이 많으며, 주가 상승에 대한 기대감과 관련된 내용은 확인되지 않음.</t>
+          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,90 +1371,90 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['양자암호', '보안', '트럼프']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3400</v>
+        <v>251750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.19%</t>
+          <t>'+1.31%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.34</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>58</v>
+        <v>445</v>
       </c>
       <c r="G11" t="n">
-        <v>199</v>
+        <v>1536</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>46.56</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3360</v>
+        <v>248500</v>
       </c>
       <c r="K11" t="n">
-        <v>3570</v>
+        <v>248000</v>
       </c>
       <c r="L11" t="n">
-        <v>3910</v>
+        <v>254000</v>
       </c>
       <c r="M11" t="n">
-        <v>3345</v>
+        <v>247500</v>
       </c>
       <c r="N11" t="n">
-        <v>1.34</v>
+        <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>102613462414</v>
+        <v>2018454036500</v>
       </c>
       <c r="P11" t="n">
-        <v>5100</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>966</v>
+        <v>76700</v>
       </c>
       <c r="R11" t="n">
-        <v>-31000</v>
+        <v>-720000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>754000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
+          <t>전반적으로 정치 관련 언급이 많으며, 주가 상승에 대한 기대감과 관련된 내용은 확인되지 않음.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,182 +1463,182 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '트럼프']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3540</v>
+        <v>13430</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.71%</t>
+          <t>'+0.98%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>551</v>
+        <v>288</v>
       </c>
       <c r="H12" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3515</v>
+        <v>13300</v>
       </c>
       <c r="K12" t="n">
-        <v>4120</v>
+        <v>13490</v>
       </c>
       <c r="L12" t="n">
-        <v>4140</v>
+        <v>13940</v>
       </c>
       <c r="M12" t="n">
-        <v>3505</v>
+        <v>13230</v>
       </c>
       <c r="N12" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>18386250843</v>
+        <v>17150355320</v>
       </c>
       <c r="P12" t="n">
-        <v>16110</v>
+        <v>19380</v>
       </c>
       <c r="Q12" t="n">
-        <v>2300</v>
+        <v>3200</v>
       </c>
       <c r="R12" t="n">
-        <v>-386000</v>
+        <v>-1000</v>
       </c>
       <c r="S12" t="n">
-        <v>-206000</v>
+        <v>4000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>최대주주 유한양행 언급에도 불구하고, 사기 도박판 및 개미 모집 후 주가 하락에 대한 부정적인 전망 제시.</t>
+          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['최대주주', '주가 하락', '공매도']</t>
+          <t>['주가', '호재', '투자심리']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13370</v>
+        <v>3505</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.53%</t>
+          <t>'-0.28%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="G13" t="n">
-        <v>281</v>
+        <v>583</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13300</v>
+        <v>3515</v>
       </c>
       <c r="K13" t="n">
-        <v>13490</v>
+        <v>4120</v>
       </c>
       <c r="L13" t="n">
-        <v>13940</v>
+        <v>4140</v>
       </c>
       <c r="M13" t="n">
-        <v>13230</v>
+        <v>3500</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O13" t="n">
-        <v>16987845350</v>
+        <v>18592673517</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>16110</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>2300</v>
       </c>
       <c r="R13" t="n">
-        <v>-1000</v>
+        <v>-386000</v>
       </c>
       <c r="S13" t="n">
-        <v>4000</v>
+        <v>-206000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
+          <t>최대주주 유한양행. 바이오 섹터 내 작전 세력 의혹 및 급락에 대한 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,20 +1647,20 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가', '호재', '투자심리']</t>
+          <t>['유한양행', '바이오', '작전세력']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10090</v>
+        <v>10070</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.30%</t>
+          <t>'-0.49%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F14" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G14" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="H14" t="n">
         <v>0.67</v>
@@ -1714,7 +1714,7 @@
         <v>0.6</v>
       </c>
       <c r="O14" t="n">
-        <v>117031419905</v>
+        <v>117628830085</v>
       </c>
       <c r="P14" t="n">
         <v>15960</v>
@@ -1759,184 +1759,184 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8500</v>
+        <v>5200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.28%</t>
+          <t>'-0.57%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.5</v>
+        <v>-1.39</v>
       </c>
       <c r="E15" t="n">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>418</v>
+        <v>189</v>
       </c>
       <c r="H15" t="n">
-        <v>26.66</v>
+        <v>1.29</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8610</v>
+        <v>5230</v>
       </c>
       <c r="K15" t="n">
-        <v>8600</v>
+        <v>5750</v>
       </c>
       <c r="L15" t="n">
-        <v>8610</v>
+        <v>5880</v>
       </c>
       <c r="M15" t="n">
-        <v>8430</v>
+        <v>5020</v>
       </c>
       <c r="N15" t="n">
-        <v>27.16</v>
+        <v>2.68</v>
       </c>
       <c r="O15" t="n">
-        <v>11980767150</v>
+        <v>63531112395</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>8980</v>
       </c>
       <c r="Q15" t="n">
-        <v>8120</v>
+        <v>2795</v>
       </c>
       <c r="R15" t="n">
-        <v>-492000</v>
+        <v>98000</v>
       </c>
       <c r="S15" t="n">
-        <v>-58000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>낮은 PBR 언급에도 불구, 삼성디스플레이와의 비교 및 재무 상태에 대한 우려. 외인 매도 지속.</t>
+          <t>미국 사이버보안주 강세 속 양자보안 구축 의무화 및 3기업 독점 관련 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['PBR', '재무상태']</t>
+          <t>['양자보안', '사이버보안', '독점']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5160</v>
+        <v>8490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.34%</t>
+          <t>'-1.39%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.39</v>
+        <v>-0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="G16" t="n">
-        <v>177</v>
+        <v>426</v>
       </c>
       <c r="H16" t="n">
-        <v>1.29</v>
+        <v>26.66</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>5230</v>
+        <v>8610</v>
       </c>
       <c r="K16" t="n">
-        <v>5750</v>
+        <v>8600</v>
       </c>
       <c r="L16" t="n">
-        <v>5880</v>
+        <v>8610</v>
       </c>
       <c r="M16" t="n">
-        <v>5020</v>
+        <v>8430</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>27.16</v>
       </c>
       <c r="O16" t="n">
-        <v>63188861680</v>
+        <v>12860487020</v>
       </c>
       <c r="P16" t="n">
-        <v>8980</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>2795</v>
+        <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>98000</v>
+        <v>-492000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-58000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 사이버보안주 강세 속 양자보안 구축 의무화 및 3기업 독점 관련 기대.</t>
+          <t>낮은 PBR에도 불구하고 실적 부진 및 경영진 비판. 외인 매도세 지속.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['양자보안', '사이버보안', '독점']</t>
+          <t>['PBR', '실적부진', '외인매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10420</v>
+        <v>10430</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.25%</t>
+          <t>'-2.16%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1990,7 +1990,7 @@
         <v>17.93</v>
       </c>
       <c r="O17" t="n">
-        <v>117694381110</v>
+        <v>118353117390</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31700</v>
+        <v>31650</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.31%</t>
+          <t>'-2.47%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.34</v>
       </c>
       <c r="E18" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F18" t="n">
         <v>139</v>
       </c>
       <c r="G18" t="n">
-        <v>1163</v>
+        <v>1181</v>
       </c>
       <c r="H18" t="n">
         <v>17.16</v>
@@ -2082,7 +2082,7 @@
         <v>17.5</v>
       </c>
       <c r="O18" t="n">
-        <v>9213739100</v>
+        <v>9306123475</v>
       </c>
       <c r="P18" t="n">
         <v>69200</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20200</v>
+        <v>20150</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.42%</t>
+          <t>'-2.66%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G19" t="n">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H19" t="n">
         <v>28.51</v>
@@ -2168,13 +2168,13 @@
         <v>20750</v>
       </c>
       <c r="M19" t="n">
-        <v>20200</v>
+        <v>20150</v>
       </c>
       <c r="N19" t="n">
         <v>28.9</v>
       </c>
       <c r="O19" t="n">
-        <v>29530353850</v>
+        <v>30855841575</v>
       </c>
       <c r="P19" t="n">
         <v>35350</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>LNG선 등 1.6조 수주 및 목표치 초과 달성 등 긍정적 뉴스에도 불구하고, 지속적인 주가 하락과 공매도 세력의 압박으로 투자자 불만 고조.</t>
+          <t>LNG선 등 1.6조 수주 확보. IBK 목표주가 상향 제시에도 주가 부진 및 공매도 압박.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['LNG선수주', '공매도', '목표주가']</t>
+          <t>['LNG선수주', '목표주가', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>83700</v>
+        <v>83800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.90%</t>
+          <t>'-2.78%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="F20" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G20" t="n">
-        <v>995</v>
+        <v>1017</v>
       </c>
       <c r="H20" t="n">
         <v>23.37</v>
@@ -2266,7 +2266,7 @@
         <v>23.45</v>
       </c>
       <c r="O20" t="n">
-        <v>135369532800</v>
+        <v>139076860050</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 관련 뉴스로 인한 기대감 있으나, 대미 투자 연기 및 공매도 세력의 움직임으로 주가 하락. 불신 팽배.</t>
+          <t>웨스팅하우스 지분 인수 기대와 대미 투자 연기 이슈 혼재. 공매도 세력의 압박.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '공매도', '대미투자']</t>
+          <t>['웨스팅하우스', '지분인수', '대미투자']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18550</v>
+        <v>18590</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F21" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G21" t="n">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="H21" t="n">
         <v>10.64</v>
@@ -2358,7 +2358,7 @@
         <v>10.53</v>
       </c>
       <c r="O21" t="n">
-        <v>54151991070</v>
+        <v>55454954210</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16960</v>
+        <v>16950</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.36%</t>
+          <t>'-3.42%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F22" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G22" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H22" t="n">
         <v>0.45</v>
@@ -2450,7 +2450,7 @@
         <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>159000929550</v>
+        <v>159216508315</v>
       </c>
       <c r="P22" t="n">
         <v>30550</v>
@@ -2495,31 +2495,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6080</v>
+        <v>14090</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-3.65%</t>
+          <t>'-5.94%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>102</v>
+        <v>252</v>
       </c>
       <c r="F23" t="n">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="G23" t="n">
-        <v>185</v>
+        <v>617</v>
       </c>
       <c r="H23" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,91 +2527,91 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>6310</v>
+        <v>14980</v>
       </c>
       <c r="K23" t="n">
-        <v>6390</v>
+        <v>15300</v>
       </c>
       <c r="L23" t="n">
-        <v>6450</v>
+        <v>15580</v>
       </c>
       <c r="M23" t="n">
-        <v>5630</v>
+        <v>13520</v>
       </c>
       <c r="N23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>47491085275</v>
+        <v>34745636365</v>
       </c>
       <c r="P23" t="n">
-        <v>11370</v>
+        <v>36200</v>
       </c>
       <c r="Q23" t="n">
-        <v>3300</v>
+        <v>8920</v>
       </c>
       <c r="R23" t="n">
-        <v>342000</v>
+        <v>-2000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t xml:space="preserve">미국 클래리티 법안 부결 소식에 따른 가상자산 관련주 관심 증폭. 공매도 거래량 및 외국인 순매수 데이터 혼재. 향후 주가 추세에 대한 엇갈린 전망.  </t>
+          <t>사우디 및 국제유가 상승 관련 기대감에도 불구하고, 비축유 및 FOMC 대비 등으로 인한 주가 하락 우려. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['클래리티법', '공매도', '외국인']</t>
+          <t>['국제유가', '비축유', 'FOMC']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14030</v>
+        <v>5930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.34%</t>
+          <t>'-6.02%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
       <c r="E24" t="n">
-        <v>248</v>
+        <v>102</v>
       </c>
       <c r="F24" t="n">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="G24" t="n">
-        <v>615</v>
+        <v>186</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,60 +2619,60 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>14980</v>
+        <v>6310</v>
       </c>
       <c r="K24" t="n">
-        <v>15300</v>
+        <v>6390</v>
       </c>
       <c r="L24" t="n">
-        <v>15580</v>
+        <v>6450</v>
       </c>
       <c r="M24" t="n">
-        <v>13520</v>
+        <v>5630</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O24" t="n">
-        <v>34044005225</v>
+        <v>50350344285</v>
       </c>
       <c r="P24" t="n">
-        <v>36200</v>
+        <v>11370</v>
       </c>
       <c r="Q24" t="n">
-        <v>8920</v>
+        <v>3300</v>
       </c>
       <c r="R24" t="n">
-        <v>-2000</v>
+        <v>342000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>사우디 및 국제유가 상승 관련 기대감에도 불구하고, 비축유 및 FOMC 대비 등으로 인한 주가 하락 우려. 투자 심리 위축.</t>
+          <t xml:space="preserve">미국 클래리티 법안 부결 소식에 따른 가상자산 관련주 관심 증폭. 공매도 거래량 및 외국인 순매수 데이터 혼재. 향후 주가 추세에 대한 엇갈린 전망.  </t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['국제유가', '비축유', 'FOMC']</t>
+          <t>['클래리티법', '공매도', '외국인']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>158430</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260916_14.xlsx
+++ b/data/trending_integrated_20260916_14.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F2" t="n">
         <v>154</v>
       </c>
       <c r="G2" t="n">
-        <v>1169</v>
+        <v>1204</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7461644610</v>
+        <v>7467024450</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>카카오의 인수 가능성 및 합법 카지노 사업 확장 기대. 본느 7연상 패턴 돌파 및 숏스퀴즈 전망.</t>
+          <t>카카오 인수 관련 루머 속 카지노 사업 기대감, 공매도 숏스퀴즈 및 본느 7연상 패턴 비교.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['카카오 인수', '합법 카지노', '숏스퀴즈']</t>
+          <t>['카카오 인수', '공매도 숏스퀴즈']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13790</v>
+        <v>13700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+28.88%</t>
+          <t>'+28.04%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G3" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>177863535660</v>
+        <v>178407212700</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16010</v>
+        <v>16000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.22%</t>
+          <t>'+13.15%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="F4" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G4" t="n">
-        <v>1944</v>
+        <v>2004</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>609502928935</v>
+        <v>616661287695</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4405</v>
+        <v>4380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.92%</t>
+          <t>'+6.31%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F5" t="n">
         <v>110</v>
       </c>
       <c r="G5" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>313456230529</v>
+        <v>315108179411</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광케이블 관련 기대감 속 지지선 확보. 종가 예상 및 향후 상승 기대.</t>
+          <t>광케이블 관련 호재 기대감 속 상한가 및 급등 예상, 4천원 지지선 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광케이블', '지지선', '종가']</t>
+          <t>['광케이블', '상한가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>193700</v>
+        <v>194200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.53%</t>
+          <t>'+3.79%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="H6" t="n">
         <v>75.66</v>
@@ -978,7 +978,7 @@
         <v>75.67</v>
       </c>
       <c r="O6" t="n">
-        <v>528693680200</v>
+        <v>540324621050</v>
       </c>
       <c r="P6" t="n">
         <v>243500</v>
@@ -1023,92 +1023,92 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7130</v>
+        <v>1736000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.33%</t>
+          <t>'+2.72%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>82</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>464</v>
       </c>
       <c r="G7" t="n">
-        <v>67</v>
+        <v>1830</v>
       </c>
       <c r="H7" t="n">
-        <v>0.79</v>
+        <v>50.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6900</v>
+        <v>1690000</v>
       </c>
       <c r="K7" t="n">
-        <v>6770</v>
+        <v>1686000</v>
       </c>
       <c r="L7" t="n">
-        <v>8590</v>
+        <v>1750000</v>
       </c>
       <c r="M7" t="n">
-        <v>6660</v>
+        <v>1686000</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7</v>
+        <v>50.27</v>
       </c>
       <c r="O7" t="n">
-        <v>79882537165</v>
+        <v>3472466845500</v>
       </c>
       <c r="P7" t="n">
-        <v>10360</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>2965</v>
+        <v>331500</v>
       </c>
       <c r="R7" t="n">
-        <v>74000</v>
+        <v>-46000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>외인 선물 대규모 매수세 유입 및 자사주 매입 관련 내용 언급, 단기 급등 및 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['외인 선물', '자사주 매입']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1130,10 +1130,10 @@
         <v>0.82</v>
       </c>
       <c r="E8" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>164</v>
@@ -1162,7 +1162,7 @@
         <v>0.84</v>
       </c>
       <c r="O8" t="n">
-        <v>126644075343</v>
+        <v>127323756334</v>
       </c>
       <c r="P8" t="n">
         <v>6190</v>
@@ -1207,162 +1207,162 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1735000</v>
+        <v>7080</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.66%</t>
+          <t>'+2.61%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>82</v>
       </c>
       <c r="F9" t="n">
-        <v>469</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>1946</v>
+        <v>74</v>
       </c>
       <c r="H9" t="n">
-        <v>50.2</v>
+        <v>0.79</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1690000</v>
+        <v>6900</v>
       </c>
       <c r="K9" t="n">
-        <v>1686000</v>
+        <v>6770</v>
       </c>
       <c r="L9" t="n">
-        <v>1750000</v>
+        <v>8590</v>
       </c>
       <c r="M9" t="n">
-        <v>1686000</v>
+        <v>6660</v>
       </c>
       <c r="N9" t="n">
-        <v>50.27</v>
+        <v>0.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3360563132500</v>
+        <v>80257133220</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>10360</v>
       </c>
       <c r="Q9" t="n">
-        <v>331500</v>
+        <v>2965</v>
       </c>
       <c r="R9" t="n">
-        <v>-46000</v>
+        <v>74000</v>
       </c>
       <c r="S9" t="n">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외인 선물 대규모 매수 속 자사주 매입 및 소각 기대감. 그러나 '내가 팔면 오르는' 패턴 반복.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['자사주매입', '자사주소각', '외인선물']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3430</v>
+        <v>13530</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.08%</t>
+          <t>'+1.73%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.34</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>203</v>
+        <v>303</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3360</v>
+        <v>13300</v>
       </c>
       <c r="K10" t="n">
-        <v>3570</v>
+        <v>13490</v>
       </c>
       <c r="L10" t="n">
-        <v>3910</v>
+        <v>13940</v>
       </c>
       <c r="M10" t="n">
-        <v>3345</v>
+        <v>13230</v>
       </c>
       <c r="N10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>103044712109</v>
+        <v>17373554665</v>
       </c>
       <c r="P10" t="n">
-        <v>5100</v>
+        <v>19380</v>
       </c>
       <c r="Q10" t="n">
-        <v>966</v>
+        <v>3200</v>
       </c>
       <c r="R10" t="n">
-        <v>-31000</v>
+        <v>-1000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
+          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '트럼프']</t>
+          <t>['주가', '호재', '투자심리']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>251750</v>
+        <v>252000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.31%</t>
+          <t>'+1.41%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="G11" t="n">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="H11" t="n">
         <v>46.56</v>
@@ -1438,7 +1438,7 @@
         <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>2018454036500</v>
+        <v>2089269315250</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>전반적으로 정치 관련 언급이 많으며, 주가 상승에 대한 기대감과 관련된 내용은 확인되지 않음.</t>
+          <t>정치적 이슈 언급 속 연말 최고점 돌파 및 주가 상승 기대, 이재용 구속 관련 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13430</v>
+        <v>5270</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.98%</t>
+          <t>'+0.76%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-1.39</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>288</v>
+        <v>197</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13300</v>
+        <v>5230</v>
       </c>
       <c r="K12" t="n">
-        <v>13490</v>
+        <v>5750</v>
       </c>
       <c r="L12" t="n">
-        <v>13940</v>
+        <v>5880</v>
       </c>
       <c r="M12" t="n">
-        <v>13230</v>
+        <v>5020</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O12" t="n">
-        <v>17150355320</v>
+        <v>64240062975</v>
       </c>
       <c r="P12" t="n">
-        <v>19380</v>
+        <v>8980</v>
       </c>
       <c r="Q12" t="n">
-        <v>3200</v>
+        <v>2795</v>
       </c>
       <c r="R12" t="n">
-        <v>-1000</v>
+        <v>98000</v>
       </c>
       <c r="S12" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
+          <t>미국 사이버보안주 강세 속 양자보안 구축 의무화 및 3기업 독점 관련 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가', '호재', '투자심리']</t>
+          <t>['양자보안', '사이버보안', '독점']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3505</v>
+        <v>3530</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.28%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F13" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>583</v>
+        <v>618</v>
       </c>
       <c r="H13" t="n">
         <v>3.11</v>
@@ -1616,13 +1616,13 @@
         <v>4140</v>
       </c>
       <c r="M13" t="n">
-        <v>3500</v>
+        <v>3485</v>
       </c>
       <c r="N13" t="n">
         <v>3.16</v>
       </c>
       <c r="O13" t="n">
-        <v>18592673517</v>
+        <v>18997873515</v>
       </c>
       <c r="P13" t="n">
         <v>16110</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>최대주주 유한양행. 바이오 섹터 내 작전 세력 의혹 및 급락에 대한 우려.</t>
+          <t>사기 도박판 및 개미 털기 의혹 제기, 주가 급락 및 2천원대 회귀 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['유한양행', '바이오', '작전세력']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,79 +1667,79 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10070</v>
+        <v>3365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.49%</t>
+          <t>'+0.15%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.34</v>
       </c>
       <c r="E14" t="n">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="F14" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="G14" t="n">
-        <v>320</v>
+        <v>204</v>
       </c>
       <c r="H14" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10120</v>
+        <v>3360</v>
       </c>
       <c r="K14" t="n">
-        <v>10190</v>
+        <v>3570</v>
       </c>
       <c r="L14" t="n">
-        <v>10920</v>
+        <v>3910</v>
       </c>
       <c r="M14" t="n">
-        <v>9790</v>
+        <v>3345</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6</v>
+        <v>1.34</v>
       </c>
       <c r="O14" t="n">
-        <v>117628830085</v>
+        <v>103636589581</v>
       </c>
       <c r="P14" t="n">
-        <v>15960</v>
+        <v>5100</v>
       </c>
       <c r="Q14" t="n">
-        <v>3500</v>
+        <v>966</v>
       </c>
       <c r="R14" t="n">
-        <v>-59000</v>
+        <v>-31000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미프진 독점 공급 계약 관련 도입 시점 불확실 속 기대감 혼재. 주가 변동성 큼.</t>
+          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['미프진', '독점 공급', '도입']</t>
+          <t>['양자암호', '보안', '트럼프']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,91 +1747,91 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5200</v>
+        <v>10110</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.57%</t>
+          <t>'-0.10%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1.39</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="G15" t="n">
-        <v>189</v>
+        <v>321</v>
       </c>
       <c r="H15" t="n">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>5230</v>
+        <v>10120</v>
       </c>
       <c r="K15" t="n">
-        <v>5750</v>
+        <v>10190</v>
       </c>
       <c r="L15" t="n">
-        <v>5880</v>
+        <v>10920</v>
       </c>
       <c r="M15" t="n">
-        <v>5020</v>
+        <v>9790</v>
       </c>
       <c r="N15" t="n">
-        <v>2.68</v>
+        <v>0.6</v>
       </c>
       <c r="O15" t="n">
-        <v>63531112395</v>
+        <v>118058819475</v>
       </c>
       <c r="P15" t="n">
-        <v>8980</v>
+        <v>15960</v>
       </c>
       <c r="Q15" t="n">
-        <v>2795</v>
+        <v>3500</v>
       </c>
       <c r="R15" t="n">
-        <v>98000</v>
+        <v>-59000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 사이버보안주 강세 속 양자보안 구축 의무화 및 3기업 독점 관련 기대.</t>
+          <t>미프진 독점 공급 계약 관련 도입 시점 불확실 속 기대감 혼재. 주가 변동성 큼.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['양자보안', '사이버보안', '독점']</t>
+          <t>['미프진', '독점 공급', '도입']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8490</v>
+        <v>8460</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.39%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F16" t="n">
         <v>61</v>
       </c>
       <c r="G16" t="n">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="H16" t="n">
         <v>26.66</v>
@@ -1898,7 +1898,7 @@
         <v>27.16</v>
       </c>
       <c r="O16" t="n">
-        <v>12860487020</v>
+        <v>13686182010</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>낮은 PBR에도 불구하고 실적 부진 및 경영진 비판. 외인 매도세 지속.</t>
+          <t>부진한 실적 및 낮은 PBR 언급, 삼성디스플레이와의 비교 속 경영진 성과급 문제 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['PBR', '실적부진', '외인매도']</t>
+          <t>['PBR', '실적']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10430</v>
+        <v>10460</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.16%</t>
+          <t>'-1.88%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>66</v>
       </c>
       <c r="G17" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H17" t="n">
         <v>19.22</v>
@@ -1990,7 +1990,7 @@
         <v>17.93</v>
       </c>
       <c r="O17" t="n">
-        <v>118353117390</v>
+        <v>118727864910</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31650</v>
+        <v>31750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.47%</t>
+          <t>'-2.16%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.34</v>
       </c>
       <c r="E18" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F18" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G18" t="n">
-        <v>1181</v>
+        <v>1192</v>
       </c>
       <c r="H18" t="n">
         <v>17.16</v>
@@ -2082,7 +2082,7 @@
         <v>17.5</v>
       </c>
       <c r="O18" t="n">
-        <v>9306123475</v>
+        <v>9454025200</v>
       </c>
       <c r="P18" t="n">
         <v>69200</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20150</v>
+        <v>20200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.66%</t>
+          <t>'-2.42%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F19" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G19" t="n">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="H19" t="n">
         <v>28.51</v>
@@ -2174,7 +2174,7 @@
         <v>28.9</v>
       </c>
       <c r="O19" t="n">
-        <v>30855841575</v>
+        <v>32809423750</v>
       </c>
       <c r="P19" t="n">
         <v>35350</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>83800</v>
+        <v>84000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.78%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F20" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G20" t="n">
-        <v>1017</v>
+        <v>1031</v>
       </c>
       <c r="H20" t="n">
         <v>23.37</v>
@@ -2266,7 +2266,7 @@
         <v>23.45</v>
       </c>
       <c r="O20" t="n">
-        <v>139076860050</v>
+        <v>142533684700</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18590</v>
+        <v>18600</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.82%</t>
+          <t>'-2.77%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F21" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G21" t="n">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H21" t="n">
         <v>10.64</v>
@@ -2358,7 +2358,7 @@
         <v>10.53</v>
       </c>
       <c r="O21" t="n">
-        <v>55454954210</v>
+        <v>56800594075</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16950</v>
+        <v>16890</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.42%</t>
+          <t>'-3.76%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F22" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G22" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H22" t="n">
         <v>0.45</v>
@@ -2450,7 +2450,7 @@
         <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>159216508315</v>
+        <v>159623976030</v>
       </c>
       <c r="P22" t="n">
         <v>30550</v>
@@ -2495,31 +2495,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14090</v>
+        <v>5960</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-5.94%</t>
+          <t>'-5.55%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
       <c r="E23" t="n">
-        <v>252</v>
+        <v>105</v>
       </c>
       <c r="F23" t="n">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="G23" t="n">
-        <v>617</v>
+        <v>190</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,91 +2527,91 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>14980</v>
+        <v>6310</v>
       </c>
       <c r="K23" t="n">
-        <v>15300</v>
+        <v>6390</v>
       </c>
       <c r="L23" t="n">
-        <v>15580</v>
+        <v>6450</v>
       </c>
       <c r="M23" t="n">
-        <v>13520</v>
+        <v>5630</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>34745636365</v>
+        <v>51033972405</v>
       </c>
       <c r="P23" t="n">
-        <v>36200</v>
+        <v>11370</v>
       </c>
       <c r="Q23" t="n">
-        <v>8920</v>
+        <v>3300</v>
       </c>
       <c r="R23" t="n">
-        <v>-2000</v>
+        <v>342000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>사우디 및 국제유가 상승 관련 기대감에도 불구하고, 비축유 및 FOMC 대비 등으로 인한 주가 하락 우려. 투자 심리 위축.</t>
+          <t xml:space="preserve">미국 클래리티 법안 부결 소식에 따른 가상자산 관련주 관심 증폭. 공매도 거래량 및 외국인 순매수 데이터 혼재. 향후 주가 추세에 대한 엇갈린 전망.  </t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['국제유가', '비축유', 'FOMC']</t>
+          <t>['클래리티법', '공매도', '외국인']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5930</v>
+        <v>14140</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.02%</t>
+          <t>'-5.61%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>102</v>
+        <v>253</v>
       </c>
       <c r="F24" t="n">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="G24" t="n">
-        <v>186</v>
+        <v>621</v>
       </c>
       <c r="H24" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,60 +2619,60 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6310</v>
+        <v>14980</v>
       </c>
       <c r="K24" t="n">
-        <v>6390</v>
+        <v>15300</v>
       </c>
       <c r="L24" t="n">
-        <v>6450</v>
+        <v>15580</v>
       </c>
       <c r="M24" t="n">
-        <v>5630</v>
+        <v>13520</v>
       </c>
       <c r="N24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>50350344285</v>
+        <v>35102948460</v>
       </c>
       <c r="P24" t="n">
-        <v>11370</v>
+        <v>36200</v>
       </c>
       <c r="Q24" t="n">
-        <v>3300</v>
+        <v>8920</v>
       </c>
       <c r="R24" t="n">
-        <v>342000</v>
+        <v>-2000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t xml:space="preserve">미국 클래리티 법안 부결 소식에 따른 가상자산 관련주 관심 증폭. 공매도 거래량 및 외국인 순매수 데이터 혼재. 향후 주가 추세에 대한 엇갈린 전망.  </t>
+          <t>사우디 및 국제유가 상승 관련 기대감에도 불구하고, 비축유 및 FOMC 대비 등으로 인한 주가 하락 우려. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['클래리티법', '공매도', '외국인']</t>
+          <t>['국제유가', '비축유', 'FOMC']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>024060</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260916_14.xlsx
+++ b/data/trending_integrated_20260916_14.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F2" t="n">
         <v>154</v>
       </c>
       <c r="G2" t="n">
-        <v>1204</v>
+        <v>1215</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7467024450</v>
+        <v>7483021890</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13700</v>
+        <v>13640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+28.04%</t>
+          <t>'+27.48%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
         <v>82</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>178407212700</v>
+        <v>178872448915</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -711,7 +711,7 @@
         <v>4600</v>
       </c>
       <c r="R3" t="n">
-        <v>21000</v>
+        <v>32000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16000</v>
+        <v>16040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.15%</t>
+          <t>'+13.44%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="F4" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G4" t="n">
-        <v>2004</v>
+        <v>2042</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>616661287695</v>
+        <v>621550008625</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -803,10 +803,10 @@
         <v>1272</v>
       </c>
       <c r="R4" t="n">
-        <v>1050000</v>
+        <v>1127000</v>
       </c>
       <c r="S4" t="n">
-        <v>41000</v>
+        <v>46000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4380</v>
+        <v>4370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.31%</t>
+          <t>'+6.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F5" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G5" t="n">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>315108179411</v>
+        <v>316896764345</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -895,23 +895,23 @@
         <v>592</v>
       </c>
       <c r="R5" t="n">
-        <v>-119000</v>
+        <v>-100000</v>
       </c>
       <c r="S5" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광케이블 관련 호재 기대감 속 상한가 및 급등 예상, 4천원 지지선 언급.</t>
+          <t>광케이블 관련 이슈와 함께 당일 주가 상승에 대한 기대감이 나타남. 단기적인 가격 움직임에 대한 언급이 있으나, 구체적인 호재 정보는 부족함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광케이블', '상한가']</t>
+          <t>['광케이블', '추세', '상승']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>194200</v>
+        <v>194100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.79%</t>
+          <t>'+3.74%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="H6" t="n">
         <v>75.66</v>
@@ -978,7 +978,7 @@
         <v>75.67</v>
       </c>
       <c r="O6" t="n">
-        <v>540324621050</v>
+        <v>550820924200</v>
       </c>
       <c r="P6" t="n">
         <v>243500</v>
@@ -987,10 +987,10 @@
         <v>61800</v>
       </c>
       <c r="R6" t="n">
-        <v>-216000</v>
+        <v>-146000</v>
       </c>
       <c r="S6" t="n">
-        <v>33000</v>
+        <v>16000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1023,215 +1023,215 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1736000</v>
+        <v>7130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.72%</t>
+          <t>'+3.33%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
-        <v>464</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>1830</v>
+        <v>64</v>
       </c>
       <c r="H7" t="n">
-        <v>50.2</v>
+        <v>0.79</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1690000</v>
+        <v>6900</v>
       </c>
       <c r="K7" t="n">
-        <v>1686000</v>
+        <v>6770</v>
       </c>
       <c r="L7" t="n">
-        <v>1750000</v>
+        <v>8590</v>
       </c>
       <c r="M7" t="n">
-        <v>1686000</v>
+        <v>6660</v>
       </c>
       <c r="N7" t="n">
-        <v>50.27</v>
+        <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3472466845500</v>
+        <v>80553285880</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>10360</v>
       </c>
       <c r="Q7" t="n">
-        <v>331500</v>
+        <v>2965</v>
       </c>
       <c r="R7" t="n">
-        <v>-46000</v>
+        <v>87000</v>
       </c>
       <c r="S7" t="n">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외인 선물 대규모 매수세 유입 및 자사주 매입 관련 내용 언급, 단기 급등 및 조정 가능성 시사.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외인 선물', '자사주 매입']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>씨피시스템</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4620</v>
+        <v>1738000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.67%</t>
+          <t>'+2.84%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.82</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>104</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>464</v>
       </c>
       <c r="G8" t="n">
-        <v>164</v>
+        <v>1800</v>
       </c>
       <c r="H8" t="n">
-        <v>1.66</v>
+        <v>50.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4500</v>
+        <v>1690000</v>
       </c>
       <c r="K8" t="n">
-        <v>4480</v>
+        <v>1686000</v>
       </c>
       <c r="L8" t="n">
-        <v>5400</v>
+        <v>1750000</v>
       </c>
       <c r="M8" t="n">
-        <v>4290</v>
+        <v>1686000</v>
       </c>
       <c r="N8" t="n">
-        <v>0.84</v>
+        <v>50.27</v>
       </c>
       <c r="O8" t="n">
-        <v>127323756334</v>
+        <v>3585665415500</v>
       </c>
       <c r="P8" t="n">
-        <v>6190</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>1938</v>
+        <v>331500</v>
       </c>
       <c r="R8" t="n">
-        <v>-310000</v>
+        <v>-16000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성과의 4381억 공급 계약 사실 기반, 높은 잠재력과 매집 정황 언급. 10000원 직행 기대.</t>
+          <t>외인 선물 대규모 매수세 유입 및 자사주 매입 관련 내용 언급, 단기 급등 및 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공급계약', '삼성', '매집']</t>
+          <t>['외인 선물', '자사주 매입']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>413630</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>씨피시스템</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7080</v>
+        <v>4610</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.61%</t>
+          <t>'+2.44%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.09</v>
+        <v>0.82</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="H9" t="n">
-        <v>0.79</v>
+        <v>1.66</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6900</v>
+        <v>4500</v>
       </c>
       <c r="K9" t="n">
-        <v>6770</v>
+        <v>4480</v>
       </c>
       <c r="L9" t="n">
-        <v>8590</v>
+        <v>5400</v>
       </c>
       <c r="M9" t="n">
-        <v>6660</v>
+        <v>4290</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="O9" t="n">
-        <v>80257133220</v>
+        <v>127881450375</v>
       </c>
       <c r="P9" t="n">
-        <v>10360</v>
+        <v>6190</v>
       </c>
       <c r="Q9" t="n">
-        <v>2965</v>
+        <v>1938</v>
       </c>
       <c r="R9" t="n">
-        <v>74000</v>
+        <v>-302000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>삼성과의 4381억 공급 계약 사실 기반, 높은 잠재력과 매집 정황 언급. 10000원 직행 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['공급계약', '삼성', '매집']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>413630</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13530</v>
+        <v>13580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.73%</t>
+          <t>'+2.11%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>17373554665</v>
+        <v>17695657115</v>
       </c>
       <c r="P10" t="n">
         <v>19380</v>
@@ -1355,7 +1355,7 @@
         <v>3200</v>
       </c>
       <c r="R10" t="n">
-        <v>-1000</v>
+        <v>17000</v>
       </c>
       <c r="S10" t="n">
         <v>4000</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252000</v>
+        <v>251750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.41%</t>
+          <t>'+1.31%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G11" t="n">
-        <v>1538</v>
+        <v>1541</v>
       </c>
       <c r="H11" t="n">
         <v>46.56</v>
@@ -1438,7 +1438,7 @@
         <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>2089269315250</v>
+        <v>2154145444750</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1447,14 +1447,14 @@
         <v>76700</v>
       </c>
       <c r="R11" t="n">
-        <v>-720000</v>
+        <v>-933000</v>
       </c>
       <c r="S11" t="n">
-        <v>754000</v>
+        <v>841000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈 언급 속 연말 최고점 돌파 및 주가 상승 기대, 이재용 구속 관련 언급.</t>
+          <t>정치적 이슈와 관련된 내용이 주를 이루며, 주가 상승 및 하락에 대한 다양한 예측과 언급이 있으나 구체적인 근거는 부족함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['이재명', '총선', '주가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1498,13 +1498,13 @@
         <v>-1.39</v>
       </c>
       <c r="E12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
         <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H12" t="n">
         <v>1.29</v>
@@ -1530,7 +1530,7 @@
         <v>2.68</v>
       </c>
       <c r="O12" t="n">
-        <v>64240062975</v>
+        <v>65420175100</v>
       </c>
       <c r="P12" t="n">
         <v>8980</v>
@@ -1539,7 +1539,7 @@
         <v>2795</v>
       </c>
       <c r="R12" t="n">
-        <v>98000</v>
+        <v>88000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3530</v>
+        <v>10130</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.43%</t>
+          <t>'+0.10%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F13" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G13" t="n">
-        <v>618</v>
+        <v>322</v>
       </c>
       <c r="H13" t="n">
-        <v>3.11</v>
+        <v>0.67</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3515</v>
+        <v>10120</v>
       </c>
       <c r="K13" t="n">
-        <v>4120</v>
+        <v>10190</v>
       </c>
       <c r="L13" t="n">
-        <v>4140</v>
+        <v>10920</v>
       </c>
       <c r="M13" t="n">
-        <v>3485</v>
+        <v>9790</v>
       </c>
       <c r="N13" t="n">
-        <v>3.16</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="n">
-        <v>18997873515</v>
+        <v>118402234275</v>
       </c>
       <c r="P13" t="n">
-        <v>16110</v>
+        <v>15960</v>
       </c>
       <c r="Q13" t="n">
-        <v>2300</v>
+        <v>3500</v>
       </c>
       <c r="R13" t="n">
-        <v>-386000</v>
+        <v>-21000</v>
       </c>
       <c r="S13" t="n">
-        <v>-206000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>사기 도박판 및 개미 털기 의혹 제기, 주가 급락 및 2천원대 회귀 가능성 언급.</t>
+          <t>미프진 독점 공급 계약 관련 도입 시점 불확실 속 기대감 혼재. 주가 변동성 큼.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['미프진', '독점 공급', '도입']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3365</v>
+        <v>3475</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.15%</t>
+          <t>'-1.14%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1.34</v>
+        <v>-0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="F14" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="G14" t="n">
-        <v>204</v>
+        <v>631</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3360</v>
+        <v>3515</v>
       </c>
       <c r="K14" t="n">
-        <v>3570</v>
+        <v>4120</v>
       </c>
       <c r="L14" t="n">
-        <v>3910</v>
+        <v>4140</v>
       </c>
       <c r="M14" t="n">
-        <v>3345</v>
+        <v>3455</v>
       </c>
       <c r="N14" t="n">
-        <v>1.34</v>
+        <v>3.16</v>
       </c>
       <c r="O14" t="n">
-        <v>103636589581</v>
+        <v>19332996973</v>
       </c>
       <c r="P14" t="n">
-        <v>5100</v>
+        <v>16110</v>
       </c>
       <c r="Q14" t="n">
-        <v>966</v>
+        <v>2300</v>
       </c>
       <c r="R14" t="n">
-        <v>-31000</v>
+        <v>-341000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-313000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
+          <t>사기 도박판 및 개미 털기 의혹 제기, 주가 급락 및 2천원대 회귀 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,51 +1739,51 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '트럼프']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10110</v>
+        <v>8470</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.10%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F15" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>321</v>
+        <v>449</v>
       </c>
       <c r="H15" t="n">
-        <v>0.67</v>
+        <v>26.66</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>10120</v>
+        <v>8610</v>
       </c>
       <c r="K15" t="n">
-        <v>10190</v>
+        <v>8600</v>
       </c>
       <c r="L15" t="n">
-        <v>10920</v>
+        <v>8610</v>
       </c>
       <c r="M15" t="n">
-        <v>9790</v>
+        <v>8430</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6</v>
+        <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>118058819475</v>
+        <v>13868456770</v>
       </c>
       <c r="P15" t="n">
-        <v>15960</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>3500</v>
+        <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>-59000</v>
+        <v>-558000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-58000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미프진 독점 공급 계약 관련 도입 시점 불확실 속 기대감 혼재. 주가 변동성 큼.</t>
+          <t>낮은 PBR에도 불구하고 실적 부진과 경영진에 대한 불만이 제기됨. 키움증권 리포트를 언급하나, 전반적으로 부정적인 투자 심리를 나타냄.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['미프진', '독점 공급', '도입']</t>
+          <t>['PBR', '실적', '경영진']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8460</v>
+        <v>10470</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-1.78%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.5</v>
+        <v>1.29</v>
       </c>
       <c r="E16" t="n">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="F16" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G16" t="n">
-        <v>436</v>
+        <v>172</v>
       </c>
       <c r="H16" t="n">
-        <v>26.66</v>
+        <v>19.22</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,244 +1883,244 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8610</v>
+        <v>10660</v>
       </c>
       <c r="K16" t="n">
-        <v>8600</v>
+        <v>10500</v>
       </c>
       <c r="L16" t="n">
-        <v>8610</v>
+        <v>10900</v>
       </c>
       <c r="M16" t="n">
-        <v>8430</v>
+        <v>10060</v>
       </c>
       <c r="N16" t="n">
-        <v>27.16</v>
+        <v>17.93</v>
       </c>
       <c r="O16" t="n">
-        <v>13686182010</v>
+        <v>119136436950</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>22450</v>
       </c>
       <c r="Q16" t="n">
-        <v>8120</v>
+        <v>1760</v>
       </c>
       <c r="R16" t="n">
-        <v>-492000</v>
+        <v>-467000</v>
       </c>
       <c r="S16" t="n">
-        <v>-58000</v>
+        <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>부진한 실적 및 낮은 PBR 언급, 삼성디스플레이와의 비교 속 경영진 성과급 문제 제기.</t>
+          <t>연기금 순매수세 유입. 투주 물량 소화 중이나 주가 상승 모멘텀 불확실.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['PBR', '실적']</t>
+          <t>['연기금', '순매수', '투주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10460</v>
+        <v>31800</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.88%</t>
+          <t>'-2.00%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.29</v>
+        <v>-0.34</v>
       </c>
       <c r="E17" t="n">
-        <v>106</v>
+        <v>225</v>
       </c>
       <c r="F17" t="n">
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="G17" t="n">
-        <v>171</v>
+        <v>1204</v>
       </c>
       <c r="H17" t="n">
-        <v>19.22</v>
+        <v>17.16</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10660</v>
+        <v>32450</v>
       </c>
       <c r="K17" t="n">
-        <v>10500</v>
+        <v>32850</v>
       </c>
       <c r="L17" t="n">
-        <v>10900</v>
+        <v>32850</v>
       </c>
       <c r="M17" t="n">
-        <v>10060</v>
+        <v>30900</v>
       </c>
       <c r="N17" t="n">
-        <v>17.93</v>
+        <v>17.5</v>
       </c>
       <c r="O17" t="n">
-        <v>118727864910</v>
+        <v>9592491900</v>
       </c>
       <c r="P17" t="n">
-        <v>22450</v>
+        <v>69200</v>
       </c>
       <c r="Q17" t="n">
-        <v>1760</v>
+        <v>24150</v>
       </c>
       <c r="R17" t="n">
-        <v>-475000</v>
+        <v>-91000</v>
       </c>
       <c r="S17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>연기금 순매수세 유입. 투주 물량 소화 중이나 주가 상승 모멘텀 불확실.</t>
+          <t>담관암, 간암 FDA 순차 승인 기대감 속, 유럽 신약 신청 시점에 대한 의구심 및 과거 실패 사례 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['연기금', '순매수', '투주']</t>
+          <t>['FDA', '신약', '담관암']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31750</v>
+        <v>18630</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.16%</t>
+          <t>'-2.61%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.34</v>
+        <v>0.11</v>
       </c>
       <c r="E18" t="n">
-        <v>223</v>
+        <v>119</v>
       </c>
       <c r="F18" t="n">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="G18" t="n">
-        <v>1192</v>
+        <v>443</v>
       </c>
       <c r="H18" t="n">
-        <v>17.16</v>
+        <v>10.64</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>32450</v>
+        <v>19130</v>
       </c>
       <c r="K18" t="n">
-        <v>32850</v>
+        <v>19160</v>
       </c>
       <c r="L18" t="n">
-        <v>32850</v>
+        <v>19340</v>
       </c>
       <c r="M18" t="n">
-        <v>30900</v>
+        <v>18330</v>
       </c>
       <c r="N18" t="n">
-        <v>17.5</v>
+        <v>10.53</v>
       </c>
       <c r="O18" t="n">
-        <v>9454025200</v>
+        <v>58045565110</v>
       </c>
       <c r="P18" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>-83000</v>
+        <v>-59000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-140000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>담관암, 간암 FDA 순차 승인 기대감 속, 유럽 신약 신청 시점에 대한 의구심 및 과거 실패 사례 언급.</t>
+          <t>대차해지 운동 독려하며 주가 조작 의혹 제기. 2만 원 돌파 및 10만 원 이상 상승 기대.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['FDA', '신약', '담관암']</t>
+          <t>['대차해지', '주가 조작', '대형 계약']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20200</v>
+        <v>20150</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.42%</t>
+          <t>'-2.66%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F19" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G19" t="n">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="H19" t="n">
         <v>28.51</v>
@@ -2174,7 +2174,7 @@
         <v>28.9</v>
       </c>
       <c r="O19" t="n">
-        <v>32809423750</v>
+        <v>33950870600</v>
       </c>
       <c r="P19" t="n">
         <v>35350</v>
@@ -2183,10 +2183,10 @@
         <v>18440</v>
       </c>
       <c r="R19" t="n">
-        <v>-677000</v>
+        <v>-1014000</v>
       </c>
       <c r="S19" t="n">
-        <v>-51000</v>
+        <v>-65000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>84000</v>
+        <v>83800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-2.78%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F20" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G20" t="n">
-        <v>1031</v>
+        <v>1041</v>
       </c>
       <c r="H20" t="n">
         <v>23.37</v>
@@ -2266,7 +2266,7 @@
         <v>23.45</v>
       </c>
       <c r="O20" t="n">
-        <v>142533684700</v>
+        <v>145857477050</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2275,10 +2275,10 @@
         <v>57000</v>
       </c>
       <c r="R20" t="n">
-        <v>-102000</v>
+        <v>-140000</v>
       </c>
       <c r="S20" t="n">
-        <v>-86000</v>
+        <v>-123000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2311,123 +2311,123 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18600</v>
+        <v>17040</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.77%</t>
+          <t>'-2.91%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="F21" t="n">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="G21" t="n">
-        <v>446</v>
+        <v>351</v>
       </c>
       <c r="H21" t="n">
-        <v>10.64</v>
+        <v>0.45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>19130</v>
+        <v>17550</v>
       </c>
       <c r="K21" t="n">
-        <v>19160</v>
+        <v>17150</v>
       </c>
       <c r="L21" t="n">
-        <v>19340</v>
+        <v>18860</v>
       </c>
       <c r="M21" t="n">
-        <v>18330</v>
+        <v>16710</v>
       </c>
       <c r="N21" t="n">
-        <v>10.53</v>
+        <v>0.35</v>
       </c>
       <c r="O21" t="n">
-        <v>56800594075</v>
+        <v>160280192185</v>
       </c>
       <c r="P21" t="n">
-        <v>40350</v>
+        <v>30550</v>
       </c>
       <c r="Q21" t="n">
-        <v>3320</v>
+        <v>6100</v>
       </c>
       <c r="R21" t="n">
-        <v>-116000</v>
+        <v>-12000</v>
       </c>
       <c r="S21" t="n">
-        <v>-90000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>대차해지 운동 독려하며 주가 조작 의혹 제기. 2만 원 돌파 및 10만 원 이상 상승 기대.</t>
+          <t>미국 보안주 상승에도 불구하고, 개미 털기 의혹과 주가 하락에 대한 불만이 제기됨. 단기적인 주가 상승 전망도 있으나, 부정적인 논조가 우세함.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['대차해지', '주가 조작', '대형 계약']</t>
+          <t>['보안주', '주가', '개미털기']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16890</v>
+        <v>3215</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.76%</t>
+          <t>'-4.32%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1</v>
+        <v>-1.34</v>
       </c>
       <c r="E22" t="n">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="F22" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="G22" t="n">
-        <v>349</v>
+        <v>210</v>
       </c>
       <c r="H22" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,60 +2435,60 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>17550</v>
+        <v>3360</v>
       </c>
       <c r="K22" t="n">
-        <v>17150</v>
+        <v>3570</v>
       </c>
       <c r="L22" t="n">
-        <v>18860</v>
+        <v>3910</v>
       </c>
       <c r="M22" t="n">
-        <v>16710</v>
+        <v>3215</v>
       </c>
       <c r="N22" t="n">
-        <v>0.35</v>
+        <v>1.34</v>
       </c>
       <c r="O22" t="n">
-        <v>159623976030</v>
+        <v>106120854281</v>
       </c>
       <c r="P22" t="n">
-        <v>30550</v>
+        <v>5100</v>
       </c>
       <c r="Q22" t="n">
-        <v>6100</v>
+        <v>966</v>
       </c>
       <c r="R22" t="n">
-        <v>-14000</v>
+        <v>-25000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 보안주 상승 및 상용화/매출 발생 기업이라는 언급이 있으나, 주가 인위적 하락 의혹 및 수급 불안정으로 인한 부정적 분위기.</t>
+          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['보안주', '상용화', '매출발생']</t>
+          <t>['양자암호', '보안', '트럼프']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>51033972405</v>
+        <v>51467766370</v>
       </c>
       <c r="P23" t="n">
         <v>11370</v>
@@ -2551,7 +2551,7 @@
         <v>3300</v>
       </c>
       <c r="R23" t="n">
-        <v>342000</v>
+        <v>337000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14140</v>
+        <v>14030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-5.61%</t>
+          <t>'-6.34%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F24" t="n">
         <v>127</v>
       </c>
       <c r="G24" t="n">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>35102948460</v>
+        <v>35490199805</v>
       </c>
       <c r="P24" t="n">
         <v>36200</v>
@@ -2643,23 +2643,23 @@
         <v>8920</v>
       </c>
       <c r="R24" t="n">
-        <v>-2000</v>
+        <v>-7000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>사우디 및 국제유가 상승 관련 기대감에도 불구하고, 비축유 및 FOMC 대비 등으로 인한 주가 하락 우려. 투자 심리 위축.</t>
+          <t>국제 유가 상승 및 미국 오일 관련주 폭등에도 불구하고, 주가 하락 추세와 FOMC 대비 등의 언급이 있어 혼조세를 보임.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['국제유가', '비축유', 'FOMC']</t>
+          <t>['국제유가', '오일', 'FOMC']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated_20260916_14.xlsx
+++ b/data/trending_integrated_20260916_14.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G2" t="n">
-        <v>1215</v>
+        <v>1227</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7483021890</v>
+        <v>7487065410</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>카카오 인수 관련 루머 속 카지노 사업 기대감, 공매도 숏스퀴즈 및 본느 7연상 패턴 비교.</t>
+          <t>카카오의 인수 가능성 및 합법 카지노 사업 확장 기대감. 공매도 숏스퀴즈 발생 가능성 언급하며 긍정적 시각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['카카오 인수', '공매도 숏스퀴즈']</t>
+          <t>['인수', '카지노', '숏스퀴즈']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13640</v>
+        <v>13630</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.48%</t>
+          <t>'+27.38%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F3" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G3" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>178872448915</v>
+        <v>179615715325</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16040</v>
+        <v>15960</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.44%</t>
+          <t>'+12.87%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="F4" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="G4" t="n">
-        <v>2042</v>
+        <v>2082</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>621550008625</v>
+        <v>625524716555</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인/기관 대규모 순매수 및 미국 자회사 수주 기대감. 10만원 목표.</t>
+          <t>외국인/기관 대량 순매수, 미국 자회사 대규모 광통신 수주 기대감. 10만원 이상 상승 전망하며 긍정적 논조.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['대량순매수', '광통신수주', '미국자회사']</t>
+          <t>['수주', '순매수', '광통신']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4370</v>
+        <v>4375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.07%</t>
+          <t>'+6.19%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>172</v>
       </c>
       <c r="F5" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G5" t="n">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>316896764345</v>
+        <v>317803385137</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광케이블 관련 이슈와 함께 당일 주가 상승에 대한 기대감이 나타남. 단기적인 가격 움직임에 대한 언급이 있으나, 구체적인 호재 정보는 부족함.</t>
+          <t>광케이블 관련 기대감 언급 있으나, 구체적인 수주나 실적 발표 없이 주가 급등락 반복. 단기 시세차익 목적 거래 성격 강함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광케이블', '추세', '상승']</t>
+          <t>['광케이블', '단차', '시세']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,70 +931,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>194100</v>
+        <v>7170</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.74%</t>
+          <t>'+3.91%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>350</v>
+        <v>65</v>
       </c>
       <c r="H6" t="n">
-        <v>75.66</v>
+        <v>0.79</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>187100</v>
+        <v>6900</v>
       </c>
       <c r="K6" t="n">
-        <v>187200</v>
+        <v>6770</v>
       </c>
       <c r="L6" t="n">
-        <v>195900</v>
+        <v>8590</v>
       </c>
       <c r="M6" t="n">
-        <v>186100</v>
+        <v>6660</v>
       </c>
       <c r="N6" t="n">
-        <v>75.67</v>
+        <v>0.7</v>
       </c>
       <c r="O6" t="n">
-        <v>550820924200</v>
+        <v>81019266700</v>
       </c>
       <c r="P6" t="n">
-        <v>243500</v>
+        <v>10360</v>
       </c>
       <c r="Q6" t="n">
-        <v>61800</v>
+        <v>2965</v>
       </c>
       <c r="R6" t="n">
-        <v>-146000</v>
+        <v>87000</v>
       </c>
       <c r="S6" t="n">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['우선주', '배당', '괴리율']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7130</v>
+        <v>194200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.33%</t>
+          <t>'+3.79%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>64</v>
+        <v>351</v>
       </c>
       <c r="H7" t="n">
-        <v>0.79</v>
+        <v>75.66</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6900</v>
+        <v>187100</v>
       </c>
       <c r="K7" t="n">
-        <v>6770</v>
+        <v>187200</v>
       </c>
       <c r="L7" t="n">
-        <v>8590</v>
+        <v>195900</v>
       </c>
       <c r="M7" t="n">
-        <v>6660</v>
+        <v>186100</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7</v>
+        <v>75.67</v>
       </c>
       <c r="O7" t="n">
-        <v>80553285880</v>
+        <v>562580847400</v>
       </c>
       <c r="P7" t="n">
-        <v>10360</v>
+        <v>243500</v>
       </c>
       <c r="Q7" t="n">
-        <v>2965</v>
+        <v>61800</v>
       </c>
       <c r="R7" t="n">
-        <v>87000</v>
+        <v>-146000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['우선주', '배당', '괴리율']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1738000</v>
+        <v>1743000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.84%</t>
+          <t>'+3.14%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="G8" t="n">
-        <v>1800</v>
+        <v>1792</v>
       </c>
       <c r="H8" t="n">
         <v>50.2</v>
@@ -1162,7 +1162,7 @@
         <v>50.27</v>
       </c>
       <c r="O8" t="n">
-        <v>3585665415500</v>
+        <v>3681536762000</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외인 선물 대규모 매수세 유입 및 자사주 매입 관련 내용 언급, 단기 급등 및 조정 가능성 시사.</t>
+          <t>외국인 선물 매수세 및 자사주 매입 관련 내용 언급. 단기적인 주가 상승 기대감 있으나, 악재 속 이유 없는 상승에 대한 의구심 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외인 선물', '자사주 매입']</t>
+          <t>['외인매수', '자사주', '기관매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4610</v>
+        <v>4630</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.44%</t>
+          <t>'+2.89%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.82</v>
       </c>
       <c r="E9" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H9" t="n">
         <v>1.66</v>
@@ -1254,7 +1254,7 @@
         <v>0.84</v>
       </c>
       <c r="O9" t="n">
-        <v>127881450375</v>
+        <v>128145783439</v>
       </c>
       <c r="P9" t="n">
         <v>6190</v>
@@ -1320,7 +1320,7 @@
         <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>17695657115</v>
+        <v>17819958180</v>
       </c>
       <c r="P10" t="n">
         <v>19380</v>
@@ -1412,7 +1412,7 @@
         <v>445</v>
       </c>
       <c r="G11" t="n">
-        <v>1541</v>
+        <v>1520</v>
       </c>
       <c r="H11" t="n">
         <v>46.56</v>
@@ -1438,7 +1438,7 @@
         <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>2154145444750</v>
+        <v>2224490964750</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 내용이 주를 이루며, 주가 상승 및 하락에 대한 다양한 예측과 언급이 있으나 구체적인 근거는 부족함.</t>
+          <t>정치적 이슈 언급 다수, 금리 인상 가능성 및 실적 관련 내용 일부 포함. 주가 관련 명확한 근거 부족.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['이재명', '총선', '주가']</t>
+          <t>['FOMC', '정치', '실적']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5270</v>
+        <v>5240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.76%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-1.39</v>
       </c>
       <c r="E12" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F12" t="n">
         <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H12" t="n">
         <v>1.29</v>
@@ -1530,7 +1530,7 @@
         <v>2.68</v>
       </c>
       <c r="O12" t="n">
-        <v>65420175100</v>
+        <v>65794405515</v>
       </c>
       <c r="P12" t="n">
         <v>8980</v>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10130</v>
+        <v>10100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.10%</t>
+          <t>'-0.20%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F13" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G13" t="n">
         <v>322</v>
@@ -1622,7 +1622,7 @@
         <v>0.6</v>
       </c>
       <c r="O13" t="n">
-        <v>118402234275</v>
+        <v>118711371265</v>
       </c>
       <c r="P13" t="n">
         <v>15960</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3475</v>
+        <v>3500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.14%</t>
+          <t>'-0.43%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F14" t="n">
         <v>84</v>
       </c>
       <c r="G14" t="n">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="H14" t="n">
         <v>3.11</v>
@@ -1708,13 +1708,13 @@
         <v>4140</v>
       </c>
       <c r="M14" t="n">
-        <v>3455</v>
+        <v>3410</v>
       </c>
       <c r="N14" t="n">
         <v>3.16</v>
       </c>
       <c r="O14" t="n">
-        <v>19332996973</v>
+        <v>19910281457</v>
       </c>
       <c r="P14" t="n">
         <v>16110</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8470</v>
+        <v>8460</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F15" t="n">
         <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>449</v>
+        <v>490</v>
       </c>
       <c r="H15" t="n">
         <v>26.66</v>
@@ -1806,7 +1806,7 @@
         <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>13868456770</v>
+        <v>14534323115</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>낮은 PBR에도 불구하고 실적 부진과 경영진에 대한 불만이 제기됨. 키움증권 리포트를 언급하나, 전반적으로 부정적인 투자 심리를 나타냄.</t>
+          <t>삼성디스플레이와 비교하며 실적 부진 및 주가 하락에 대한 부정적 의견 지배적. FLiPP 양산 기대감 있으나, 전반적인 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['PBR', '실적', '경영진']</t>
+          <t>['실적', 'PBR', '주주총회']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,215 +1851,215 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10470</v>
+        <v>31800</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.78%</t>
+          <t>'-2.00%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.29</v>
+        <v>-0.34</v>
       </c>
       <c r="E16" t="n">
-        <v>109</v>
+        <v>227</v>
       </c>
       <c r="F16" t="n">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="G16" t="n">
-        <v>172</v>
+        <v>1225</v>
       </c>
       <c r="H16" t="n">
-        <v>19.22</v>
+        <v>17.16</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>10660</v>
+        <v>32450</v>
       </c>
       <c r="K16" t="n">
-        <v>10500</v>
+        <v>32850</v>
       </c>
       <c r="L16" t="n">
-        <v>10900</v>
+        <v>32850</v>
       </c>
       <c r="M16" t="n">
-        <v>10060</v>
+        <v>30900</v>
       </c>
       <c r="N16" t="n">
-        <v>17.93</v>
+        <v>17.5</v>
       </c>
       <c r="O16" t="n">
-        <v>119136436950</v>
+        <v>9774197100</v>
       </c>
       <c r="P16" t="n">
-        <v>22450</v>
+        <v>69200</v>
       </c>
       <c r="Q16" t="n">
-        <v>1760</v>
+        <v>24150</v>
       </c>
       <c r="R16" t="n">
-        <v>-467000</v>
+        <v>-91000</v>
       </c>
       <c r="S16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>연기금 순매수세 유입. 투주 물량 소화 중이나 주가 상승 모멘텀 불확실.</t>
+          <t>담관암, 간암 FDA 순차 승인 기대감 있으나, 유럽 신청 시점 및 배경에 대한 의구심 존재. 과거 실패 사례 언급되며 부정적 전망 우세.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['연기금', '순매수', '투주']</t>
+          <t>['FDA', '담관암', '신약']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31800</v>
+        <v>10440</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.00%</t>
+          <t>'-2.06%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.34</v>
+        <v>1.29</v>
       </c>
       <c r="E17" t="n">
-        <v>225</v>
+        <v>114</v>
       </c>
       <c r="F17" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="G17" t="n">
-        <v>1204</v>
+        <v>182</v>
       </c>
       <c r="H17" t="n">
-        <v>17.16</v>
+        <v>19.22</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>32450</v>
+        <v>10660</v>
       </c>
       <c r="K17" t="n">
-        <v>32850</v>
+        <v>10500</v>
       </c>
       <c r="L17" t="n">
-        <v>32850</v>
+        <v>10900</v>
       </c>
       <c r="M17" t="n">
-        <v>30900</v>
+        <v>10060</v>
       </c>
       <c r="N17" t="n">
-        <v>17.5</v>
+        <v>17.93</v>
       </c>
       <c r="O17" t="n">
-        <v>9592491900</v>
+        <v>119694830230</v>
       </c>
       <c r="P17" t="n">
-        <v>69200</v>
+        <v>22450</v>
       </c>
       <c r="Q17" t="n">
-        <v>24150</v>
+        <v>1760</v>
       </c>
       <c r="R17" t="n">
-        <v>-91000</v>
+        <v>-467000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>담관암, 간암 FDA 순차 승인 기대감 속, 유럽 신약 신청 시점에 대한 의구심 및 과거 실패 사례 언급.</t>
+          <t>연기금 순매수세 유입. 투주 물량 소화 중이나 주가 상승 모멘텀 불확실.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['FDA', '신약', '담관암']</t>
+          <t>['연기금', '순매수', '투주']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18630</v>
+        <v>20200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.61%</t>
+          <t>'-2.42%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.11</v>
+        <v>-0.39</v>
       </c>
       <c r="E18" t="n">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="F18" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="G18" t="n">
-        <v>443</v>
+        <v>402</v>
       </c>
       <c r="H18" t="n">
-        <v>10.64</v>
+        <v>28.51</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,91 +2067,91 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19130</v>
+        <v>20700</v>
       </c>
       <c r="K18" t="n">
-        <v>19160</v>
+        <v>20750</v>
       </c>
       <c r="L18" t="n">
-        <v>19340</v>
+        <v>20750</v>
       </c>
       <c r="M18" t="n">
-        <v>18330</v>
+        <v>20150</v>
       </c>
       <c r="N18" t="n">
-        <v>10.53</v>
+        <v>28.9</v>
       </c>
       <c r="O18" t="n">
-        <v>58045565110</v>
+        <v>34610336400</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>18440</v>
       </c>
       <c r="R18" t="n">
-        <v>-59000</v>
+        <v>-1014000</v>
       </c>
       <c r="S18" t="n">
-        <v>-140000</v>
+        <v>-65000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대차해지 운동 독려하며 주가 조작 의혹 제기. 2만 원 돌파 및 10만 원 이상 상승 기대.</t>
+          <t>LNG선 등 1.6조 수주 및 목표치 초과 달성 관련 긍정적 뉴스 언급. 하지만 공매도 심화 및 주가 하락 추세에 대한 부정적 의견 다수.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['대차해지', '주가 조작', '대형 계약']</t>
+          <t>['수주', '공매도', '목표주가']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20150</v>
+        <v>83900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.66%</t>
+          <t>'-2.67%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.39</v>
+        <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>168</v>
+        <v>318</v>
       </c>
       <c r="F19" t="n">
-        <v>90</v>
+        <v>175</v>
       </c>
       <c r="G19" t="n">
-        <v>400</v>
+        <v>1048</v>
       </c>
       <c r="H19" t="n">
-        <v>28.51</v>
+        <v>23.37</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>20700</v>
+        <v>86200</v>
       </c>
       <c r="K19" t="n">
-        <v>20750</v>
+        <v>86200</v>
       </c>
       <c r="L19" t="n">
-        <v>20750</v>
+        <v>86300</v>
       </c>
       <c r="M19" t="n">
-        <v>20150</v>
+        <v>83500</v>
       </c>
       <c r="N19" t="n">
-        <v>28.9</v>
+        <v>23.45</v>
       </c>
       <c r="O19" t="n">
-        <v>33950870600</v>
+        <v>148444537250</v>
       </c>
       <c r="P19" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>18440</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-1014000</v>
+        <v>-140000</v>
       </c>
       <c r="S19" t="n">
-        <v>-65000</v>
+        <v>-123000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>LNG선 등 1.6조 수주 확보. IBK 목표주가 상향 제시에도 주가 부진 및 공매도 압박.</t>
+          <t>웨스팅하우스 지분 인수 기대와 대미 투자 연기 이슈 혼재. 공매도 세력의 압박.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['LNG선수주', '목표주가', '공매도']</t>
+          <t>['웨스팅하우스', '지분인수', '대미투자']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>83800</v>
+        <v>18590</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.78%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.08</v>
+        <v>0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>316</v>
+        <v>121</v>
       </c>
       <c r="F20" t="n">
-        <v>172</v>
+        <v>67</v>
       </c>
       <c r="G20" t="n">
-        <v>1041</v>
+        <v>446</v>
       </c>
       <c r="H20" t="n">
-        <v>23.37</v>
+        <v>10.64</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,38 +2251,38 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>86200</v>
+        <v>19130</v>
       </c>
       <c r="K20" t="n">
-        <v>86200</v>
+        <v>19160</v>
       </c>
       <c r="L20" t="n">
-        <v>86300</v>
+        <v>19340</v>
       </c>
       <c r="M20" t="n">
-        <v>83500</v>
+        <v>18330</v>
       </c>
       <c r="N20" t="n">
-        <v>23.45</v>
+        <v>10.53</v>
       </c>
       <c r="O20" t="n">
-        <v>145857477050</v>
+        <v>59284488310</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q20" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R20" t="n">
+        <v>-59000</v>
+      </c>
+      <c r="S20" t="n">
         <v>-140000</v>
       </c>
-      <c r="S20" t="n">
-        <v>-123000</v>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 기대와 대미 투자 연기 이슈 혼재. 공매도 세력의 압박.</t>
+          <t>주가 조작 의혹 및 대차 해지 운동 참여 독려. 대형 계약 임박 기대감 있으나 구체적 근거 제시 미흡.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분인수', '대미투자']</t>
+          <t>['대차해지', '주가조작', '계약']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17040</v>
+        <v>17030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.91%</t>
+          <t>'-2.96%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F21" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H21" t="n">
         <v>0.45</v>
@@ -2358,7 +2358,7 @@
         <v>0.35</v>
       </c>
       <c r="O21" t="n">
-        <v>160280192185</v>
+        <v>160627272995</v>
       </c>
       <c r="P21" t="n">
         <v>30550</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3215</v>
+        <v>3250</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-4.32%</t>
+          <t>'-3.27%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-1.34</v>
       </c>
       <c r="E22" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F22" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G22" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
         <v>1.34</v>
       </c>
       <c r="O22" t="n">
-        <v>106120854281</v>
+        <v>107199749452</v>
       </c>
       <c r="P22" t="n">
         <v>5100</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5960</v>
+        <v>5990</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-5.55%</t>
+          <t>'-5.07%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-2.04</v>
       </c>
       <c r="E23" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F23" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H23" t="n">
         <v>0.98</v>
@@ -2542,7 +2542,7 @@
         <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>51467766370</v>
+        <v>51909331965</v>
       </c>
       <c r="P23" t="n">
         <v>11370</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14030</v>
+        <v>14040</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.34%</t>
+          <t>'-6.28%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F24" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G24" t="n">
-        <v>633</v>
+        <v>654</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>35490199805</v>
+        <v>35782818910</v>
       </c>
       <c r="P24" t="n">
         <v>36200</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>국제 유가 상승 및 미국 오일 관련주 폭등에도 불구하고, 주가 하락 추세와 FOMC 대비 등의 언급이 있어 혼조세를 보임.</t>
+          <t>국제유가 상승 기대감 속에서도 주가 하락. 주포 및 CB 관련 내용 언급되며, 투자자들의 불안감 고조.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['국제유가', '오일', 'FOMC']</t>
+          <t>['국제유가', 'CB', '주포']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated_20260916_14.xlsx
+++ b/data/trending_integrated_20260916_14.xlsx
@@ -581,10 +581,10 @@
         <v>327</v>
       </c>
       <c r="F2" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G2" t="n">
-        <v>1227</v>
+        <v>1239</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7487065410</v>
+        <v>7492191810</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13630</v>
+        <v>13540</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.38%</t>
+          <t>'+26.54%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F3" t="n">
         <v>84</v>
       </c>
       <c r="G3" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>179615715325</v>
+        <v>180477414640</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15960</v>
+        <v>15940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.87%</t>
+          <t>'+12.73%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="F4" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="G4" t="n">
-        <v>2082</v>
+        <v>2132</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>625524716555</v>
+        <v>631074494660</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4375</v>
+        <v>4350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.19%</t>
+          <t>'+5.58%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F5" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G5" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>317803385137</v>
+        <v>319847450738</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광케이블 관련 기대감 언급 있으나, 구체적인 수주나 실적 발표 없이 주가 급등락 반복. 단기 시세차익 목적 거래 성격 강함.</t>
+          <t>미국 광케이블 종목의 상승과 관련하여 주가 상승에 대한 기대감이 있으나, 구체적인 사실 기반의 언급은 부족하며 단기 차익 실현 및 주가 움직임에 대한 개인적인 감정 표출이 많음.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광케이블', '단차', '시세']</t>
+          <t>['광케이블', '주가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>씨피시스템</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7170</v>
+        <v>4690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.91%</t>
+          <t>'+4.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.09</v>
+        <v>0.82</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>173</v>
       </c>
       <c r="H6" t="n">
-        <v>0.79</v>
+        <v>1.66</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6900</v>
+        <v>4500</v>
       </c>
       <c r="K6" t="n">
-        <v>6770</v>
+        <v>4480</v>
       </c>
       <c r="L6" t="n">
-        <v>8590</v>
+        <v>5400</v>
       </c>
       <c r="M6" t="n">
-        <v>6660</v>
+        <v>4290</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="O6" t="n">
-        <v>81019266700</v>
+        <v>129104223080</v>
       </c>
       <c r="P6" t="n">
-        <v>10360</v>
+        <v>6190</v>
       </c>
       <c r="Q6" t="n">
-        <v>2965</v>
+        <v>1938</v>
       </c>
       <c r="R6" t="n">
-        <v>87000</v>
+        <v>-302000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>삼성과의 4381억 공급 계약 사실 기반, 높은 잠재력과 매집 정황 언급. 10000원 직행 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['공급계약', '삼성', '매집']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>413630</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>194200</v>
+        <v>194400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.79%</t>
+          <t>'+3.90%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H7" t="n">
         <v>75.66</v>
@@ -1070,7 +1070,7 @@
         <v>75.67</v>
       </c>
       <c r="O7" t="n">
-        <v>562580847400</v>
+        <v>579181323050</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1115,184 +1115,184 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1743000</v>
+        <v>7130</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.14%</t>
+          <t>'+3.33%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>79</v>
       </c>
       <c r="F8" t="n">
-        <v>469</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>1792</v>
+        <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>50.2</v>
+        <v>0.79</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1690000</v>
+        <v>6900</v>
       </c>
       <c r="K8" t="n">
-        <v>1686000</v>
+        <v>6770</v>
       </c>
       <c r="L8" t="n">
-        <v>1750000</v>
+        <v>8590</v>
       </c>
       <c r="M8" t="n">
-        <v>1686000</v>
+        <v>6660</v>
       </c>
       <c r="N8" t="n">
-        <v>50.27</v>
+        <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3681536762000</v>
+        <v>81178140760</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>10360</v>
       </c>
       <c r="Q8" t="n">
-        <v>331500</v>
+        <v>2965</v>
       </c>
       <c r="R8" t="n">
-        <v>-16000</v>
+        <v>87000</v>
       </c>
       <c r="S8" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외국인 선물 매수세 및 자사주 매입 관련 내용 언급. 단기적인 주가 상승 기대감 있으나, 악재 속 이유 없는 상승에 대한 의구심 존재.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외인매수', '자사주', '기관매수']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>씨피시스템</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4630</v>
+        <v>1742000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.89%</t>
+          <t>'+3.08%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.82</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>468</v>
       </c>
       <c r="G9" t="n">
-        <v>171</v>
+        <v>1792</v>
       </c>
       <c r="H9" t="n">
-        <v>1.66</v>
+        <v>50.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4500</v>
+        <v>1690000</v>
       </c>
       <c r="K9" t="n">
-        <v>4480</v>
+        <v>1686000</v>
       </c>
       <c r="L9" t="n">
-        <v>5400</v>
+        <v>1750000</v>
       </c>
       <c r="M9" t="n">
-        <v>4290</v>
+        <v>1686000</v>
       </c>
       <c r="N9" t="n">
-        <v>0.84</v>
+        <v>50.27</v>
       </c>
       <c r="O9" t="n">
-        <v>128145783439</v>
+        <v>3798705904500</v>
       </c>
       <c r="P9" t="n">
-        <v>6190</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>1938</v>
+        <v>331500</v>
       </c>
       <c r="R9" t="n">
-        <v>-302000</v>
+        <v>-16000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성과의 4381억 공급 계약 사실 기반, 높은 잠재력과 매집 정황 언급. 10000원 직행 기대.</t>
+          <t>미국 내 반도체 생산 관련 인텔과의 협상 뉴스가 있으며, 자사주 매입 관련 언급도 있으나 주가 변동성에 대한 개인적인 감정 표현이 주를 이룸.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공급계약', '삼성', '매집']</t>
+          <t>['반도체', '자사주', '협상']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>413630</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13580</v>
+        <v>13570</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.11%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>17819958180</v>
+        <v>18296908450</v>
       </c>
       <c r="P10" t="n">
         <v>19380</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>251750</v>
+        <v>252750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.31%</t>
+          <t>'+1.71%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G11" t="n">
-        <v>1520</v>
+        <v>1513</v>
       </c>
       <c r="H11" t="n">
         <v>46.56</v>
@@ -1438,7 +1438,7 @@
         <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>2224490964750</v>
+        <v>2300806370500</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈 언급 다수, 금리 인상 가능성 및 실적 관련 내용 일부 포함. 주가 관련 명확한 근거 부족.</t>
+          <t>정치적 이슈와 관련된 다양한 의견이 혼재하나, 주가 상승 기대감과 관련된 구체적인 근거는 부족함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['FOMC', '정치', '실적']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5240</v>
+        <v>5270</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.19%</t>
+          <t>'+0.76%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1530,7 +1530,7 @@
         <v>2.68</v>
       </c>
       <c r="O12" t="n">
-        <v>65794405515</v>
+        <v>66135958240</v>
       </c>
       <c r="P12" t="n">
         <v>8980</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10100</v>
+        <v>10070</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.20%</t>
+          <t>'-0.49%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>82</v>
       </c>
       <c r="G13" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H13" t="n">
         <v>0.67</v>
@@ -1622,7 +1622,7 @@
         <v>0.6</v>
       </c>
       <c r="O13" t="n">
-        <v>118711371265</v>
+        <v>119246569635</v>
       </c>
       <c r="P13" t="n">
         <v>15960</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3500</v>
+        <v>3485</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.43%</t>
+          <t>'-0.85%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F14" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G14" t="n">
-        <v>641</v>
+        <v>651</v>
       </c>
       <c r="H14" t="n">
         <v>3.11</v>
@@ -1714,7 +1714,7 @@
         <v>3.16</v>
       </c>
       <c r="O14" t="n">
-        <v>19910281457</v>
+        <v>20470080486</v>
       </c>
       <c r="P14" t="n">
         <v>16110</v>
@@ -1759,83 +1759,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8460</v>
+        <v>31900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.5</v>
+        <v>-0.34</v>
       </c>
       <c r="E15" t="n">
-        <v>133</v>
+        <v>229</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="G15" t="n">
-        <v>490</v>
+        <v>1236</v>
       </c>
       <c r="H15" t="n">
-        <v>26.66</v>
+        <v>17.16</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8610</v>
+        <v>32450</v>
       </c>
       <c r="K15" t="n">
-        <v>8600</v>
+        <v>32850</v>
       </c>
       <c r="L15" t="n">
-        <v>8610</v>
+        <v>32850</v>
       </c>
       <c r="M15" t="n">
-        <v>8430</v>
+        <v>30900</v>
       </c>
       <c r="N15" t="n">
-        <v>27.16</v>
+        <v>17.5</v>
       </c>
       <c r="O15" t="n">
-        <v>14534323115</v>
+        <v>9919101200</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q15" t="n">
-        <v>8120</v>
+        <v>24150</v>
       </c>
       <c r="R15" t="n">
-        <v>-558000</v>
+        <v>-91000</v>
       </c>
       <c r="S15" t="n">
-        <v>-58000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성디스플레이와 비교하며 실적 부진 및 주가 하락에 대한 부정적 의견 지배적. FLiPP 양산 기대감 있으나, 전반적인 투자 심리 위축.</t>
+          <t>담관암, 간암 FDA 순차 승인 기대감 있으나, 유럽 신청 시점 및 배경에 대한 의구심 존재. 과거 실패 사례 언급되며 부정적 전망 우세.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적', 'PBR', '주주총회']</t>
+          <t>['FDA', '담관암', '신약']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31800</v>
+        <v>8450</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.00%</t>
+          <t>'-1.86%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.34</v>
+        <v>-0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>227</v>
+        <v>136</v>
       </c>
       <c r="F16" t="n">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>1225</v>
+        <v>497</v>
       </c>
       <c r="H16" t="n">
-        <v>17.16</v>
+        <v>26.66</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>32450</v>
+        <v>8610</v>
       </c>
       <c r="K16" t="n">
-        <v>32850</v>
+        <v>8600</v>
       </c>
       <c r="L16" t="n">
-        <v>32850</v>
+        <v>8610</v>
       </c>
       <c r="M16" t="n">
-        <v>30900</v>
+        <v>8430</v>
       </c>
       <c r="N16" t="n">
-        <v>17.5</v>
+        <v>27.16</v>
       </c>
       <c r="O16" t="n">
-        <v>9774197100</v>
+        <v>15193491485</v>
       </c>
       <c r="P16" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>24150</v>
+        <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>-91000</v>
+        <v>-558000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-58000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>담관암, 간암 FDA 순차 승인 기대감 있으나, 유럽 신청 시점 및 배경에 대한 의구심 존재. 과거 실패 사례 언급되며 부정적 전망 우세.</t>
+          <t>삼성디스플레이와 비교하며 실적 부진 및 주가 하락에 대한 부정적 의견 지배적. FLiPP 양산 기대감 있으나, 전반적인 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['FDA', '담관암', '신약']</t>
+          <t>['실적', 'PBR', '주주총회']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1958,13 +1958,13 @@
         <v>1.29</v>
       </c>
       <c r="E17" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F17" t="n">
         <v>70</v>
       </c>
       <c r="G17" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H17" t="n">
         <v>19.22</v>
@@ -1990,7 +1990,7 @@
         <v>17.93</v>
       </c>
       <c r="O17" t="n">
-        <v>119694830230</v>
+        <v>120351313350</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -2050,13 +2050,13 @@
         <v>-0.39</v>
       </c>
       <c r="E18" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F18" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G18" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H18" t="n">
         <v>28.51</v>
@@ -2082,7 +2082,7 @@
         <v>28.9</v>
       </c>
       <c r="O18" t="n">
-        <v>34610336400</v>
+        <v>36477132250</v>
       </c>
       <c r="P18" t="n">
         <v>35350</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>LNG선 등 1.6조 수주 및 목표치 초과 달성 관련 긍정적 뉴스 언급. 하지만 공매도 심화 및 주가 하락 추세에 대한 부정적 의견 다수.</t>
+          <t>1.6조 규모의 LNG선 수주 공시가 있으나, 목표치 초과 달성에 대한 긍정적 평가와 함께 IBK투자증권의 목표주가 상향 리포트도 존재. 다만, 주가 하락 및 공매도에 대한 부정적 정서가 강하게 나타남.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['수주', '공매도', '목표주가']</t>
+          <t>['LNG선', '수주', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F19" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G19" t="n">
-        <v>1048</v>
+        <v>1067</v>
       </c>
       <c r="H19" t="n">
         <v>23.37</v>
@@ -2174,7 +2174,7 @@
         <v>23.45</v>
       </c>
       <c r="O19" t="n">
-        <v>148444537250</v>
+        <v>151311445800</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2219,175 +2219,175 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18590</v>
+        <v>3270</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.82%</t>
+          <t>'-2.68%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.11</v>
+        <v>-1.34</v>
       </c>
       <c r="E20" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="F20" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G20" t="n">
-        <v>446</v>
+        <v>225</v>
       </c>
       <c r="H20" t="n">
-        <v>10.64</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>19130</v>
+        <v>3360</v>
       </c>
       <c r="K20" t="n">
-        <v>19160</v>
+        <v>3570</v>
       </c>
       <c r="L20" t="n">
-        <v>19340</v>
+        <v>3910</v>
       </c>
       <c r="M20" t="n">
-        <v>18330</v>
+        <v>3215</v>
       </c>
       <c r="N20" t="n">
-        <v>10.53</v>
+        <v>1.34</v>
       </c>
       <c r="O20" t="n">
-        <v>59284488310</v>
+        <v>107906940267</v>
       </c>
       <c r="P20" t="n">
-        <v>40350</v>
+        <v>5100</v>
       </c>
       <c r="Q20" t="n">
-        <v>3320</v>
+        <v>966</v>
       </c>
       <c r="R20" t="n">
-        <v>-59000</v>
+        <v>-25000</v>
       </c>
       <c r="S20" t="n">
-        <v>-140000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 대차 해지 운동 참여 독려. 대형 계약 임박 기대감 있으나 구체적 근거 제시 미흡.</t>
+          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['대차해지', '주가조작', '계약']</t>
+          <t>['양자암호', '보안', '트럼프']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17030</v>
+        <v>18570</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.96%</t>
+          <t>'-2.93%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="G21" t="n">
-        <v>352</v>
+        <v>457</v>
       </c>
       <c r="H21" t="n">
-        <v>0.45</v>
+        <v>10.64</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>17550</v>
+        <v>19130</v>
       </c>
       <c r="K21" t="n">
-        <v>17150</v>
+        <v>19160</v>
       </c>
       <c r="L21" t="n">
-        <v>18860</v>
+        <v>19340</v>
       </c>
       <c r="M21" t="n">
-        <v>16710</v>
+        <v>18330</v>
       </c>
       <c r="N21" t="n">
-        <v>0.35</v>
+        <v>10.53</v>
       </c>
       <c r="O21" t="n">
-        <v>160627272995</v>
+        <v>60950286955</v>
       </c>
       <c r="P21" t="n">
-        <v>30550</v>
+        <v>40350</v>
       </c>
       <c r="Q21" t="n">
-        <v>6100</v>
+        <v>3320</v>
       </c>
       <c r="R21" t="n">
-        <v>-12000</v>
+        <v>-59000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-140000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 보안주 상승에도 불구하고, 개미 털기 의혹과 주가 하락에 대한 불만이 제기됨. 단기적인 주가 상승 전망도 있으나, 부정적인 논조가 우세함.</t>
+          <t>주가 조작 의혹 및 대차 해지 운동 참여 독려. 대형 계약 임박 기대감 있으나 구체적 근거 제시 미흡.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['보안주', '주가', '개미털기']</t>
+          <t>['대차해지', '주가조작', '계약']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3250</v>
+        <v>16920</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.27%</t>
+          <t>'-3.59%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1.34</v>
+        <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>104</v>
+        <v>175</v>
       </c>
       <c r="F22" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>222</v>
+        <v>357</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,60 +2435,60 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3360</v>
+        <v>17550</v>
       </c>
       <c r="K22" t="n">
-        <v>3570</v>
+        <v>17150</v>
       </c>
       <c r="L22" t="n">
-        <v>3910</v>
+        <v>18860</v>
       </c>
       <c r="M22" t="n">
-        <v>3215</v>
+        <v>16710</v>
       </c>
       <c r="N22" t="n">
-        <v>1.34</v>
+        <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>107199749452</v>
+        <v>161126065605</v>
       </c>
       <c r="P22" t="n">
-        <v>5100</v>
+        <v>30550</v>
       </c>
       <c r="Q22" t="n">
-        <v>966</v>
+        <v>6100</v>
       </c>
       <c r="R22" t="n">
-        <v>-25000</v>
+        <v>-12000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
+          <t>미국 보안주 상승 흐름과 연관된 언급이 있으나, 주가 하락 및 개미 털기에 대한 의혹 제기 등 부정적 시각과 기대감이 혼재하며 명확한 근거 제시가 부족함.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '트럼프']</t>
+          <t>['보안주', '주가', '개미 털기']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5990</v>
+        <v>6040</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-5.07%</t>
+          <t>'-4.28%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-2.04</v>
       </c>
       <c r="E23" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G23" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H23" t="n">
         <v>0.98</v>
@@ -2542,7 +2542,7 @@
         <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>51909331965</v>
+        <v>52572262365</v>
       </c>
       <c r="P23" t="n">
         <v>11370</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14040</v>
+        <v>13960</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.28%</t>
+          <t>'-6.81%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F24" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G24" t="n">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>35782818910</v>
+        <v>36532131660</v>
       </c>
       <c r="P24" t="n">
         <v>36200</v>
